--- a/processed_ruby_restored_xlsx/sc241_みるく３：凛をベロチュー.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc241_みるく３：凛をベロチュー.ss.xlsx
@@ -499,8 +499,8 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>I glance up at the sky, nod once, and then go about my
-usual morning routine.</t>
+          <t>I glance up at the sky, nod once, and then go about
+my usual morning routine.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -879,7 +879,8 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>「Wakyaa！ Onii-chan, you're petting my head too much…！」</t>
+          <t>「Wakyaa！ Onii-chan, you're petting my head too
+much…！」</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -910,7 +911,8 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>But her face is smiling, so she's clearly enjoying it.</t>
+          <t>But her face is smiling, so she's clearly enjoying
+it.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1638,8 +1640,8 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Then Miru-chan gives a smile that mixes happiness with
-a little embarrassment.</t>
+          <t>Then Miru-chan gives a smile that mixes happiness
+with a little embarrassment.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1715,8 +1717,8 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Of course I don't plan to stop here, but at times like
-this I kinda want to tease her a little….</t>
+          <t>Of course I don't plan to stop here, but at times
+like this I kinda want to tease her a little….</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1881,8 +1883,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>When I suddenly pressed my lips to hers, Miru-chan was
-startled and clamped her mouth shut.</t>
+          <t>When I suddenly pressed my lips to hers, Miru-chan
+was startled and clamped her mouth shut.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1942,7 +1944,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Nibbling closed lips with lips, squishing them gently.</t>
+          <t>Nibbling closed lips with lips, squishing them
+gently.</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2096,7 +2099,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan gets competitive and starts licking me back.</t>
+          <t>Miru-chan gets competitive and starts licking me
+back.</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2111,8 +2115,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>For some reason it's like we're competing, but this is
-fun in its own way.</t>
+          <t>For some reason it's like we're competing, but this
+is fun in its own way.</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2854,7 +2858,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Ah... I feel like I could push her down any second...！</t>
+          <t>Ah... I feel like I could push her down any
+second...！</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3204,9 +3209,9 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan tried to hurriedly cover it up, but Rin-chan
-didn't bother and smirked as she entered the living
-room.</t>
+          <t>Miru-chan tried to hurriedly cover it up, but
+Rin-chan didn't bother and smirked as she entered the
+living room.</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3328,7 +3333,8 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>「So what were you doing all cuddled up with Niini...？」</t>
+          <t>「So what were you doing all cuddled up with
+Niini...？」</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3793,8 +3799,8 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>...It's still unclear where Rin-chan had been watching
-from.</t>
+          <t>...It's still unclear where Rin-chan had been
+watching from.</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -4554,8 +4560,8 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>No, no, no... that was completely beyond a greeting at
-this point, Miru-chan...</t>
+          <t>No, no, no... that was completely beyond a greeting
+at this point, Miru-chan...</t>
         </is>
       </c>
       <c r="C268" t="n">

--- a/processed_ruby_restored_xlsx/sc241_みるく３：凛をベロチュー.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc241_みるく３：凛をベロチュー.ss.xlsx
@@ -972,8 +972,8 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「No way. That kind of compliment sounds like you're
-talking to a puppy.」</t>
+          <t>No way. That kind of compliment sounds like you're
+talking to a puppy.</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1216,8 +1216,8 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Even though she'd been acting like that, of all days
-it seems she's in a bad mood today.</t>
+          <t>Even though they'd been acting like that, of all days
+it seems they're in a bad mood today.</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>「N-no way！ I won't forgive you！」</t>
+          <t>N-no way！ I won't forgive you！</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>「Oh no... what can I do to get you to forgive me？」</t>
+          <t>Oh no... what can I do to get you to forgive me？</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>When I suddenly pressed my lips to hers, Miru-chan
+          <t>When he suddenly pressed his lips to hers, Miru-chan
 was startled and clamped her mouth shut.</t>
         </is>
       </c>
@@ -1992,7 +1992,7 @@
       <c r="B101" s="1" t="inlineStr">
         <is>
           <t>Miru-chan had been saying no for a while, but after a
-little growl she went back at me.</t>
+little growl she went back at him.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>「Oh? You were greeting me? Greeting? MiruMiru,
+          <t>「Oh? You were greeting him? Greeting? MiruMiru,
 ohoho~...！」</t>
         </is>
       </c>
@@ -3582,8 +3582,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>She wasn't called, but it's the usual time so she
-probably came.</t>
+          <t>They weren't called, but it's their usual time so
+they probably came.</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>I wish she'd been two or three minutes later, if
+          <t>I wish they'd been two or three minutes later, if
 possible...</t>
         </is>
       </c>
